--- a/Deliverables/BOM/FLST_PCBWay BOM.xlsx
+++ b/Deliverables/BOM/FLST_PCBWay BOM.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="131">
   <si>
     <t>Designator</t>
   </si>
@@ -41,15 +41,9 @@
     <t>LCSC/Part No</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>Quantity/5 Boards</t>
-  </si>
-  <si>
     <t>LCSC/MOQ/5 Boards</t>
   </si>
   <si>
@@ -420,30 +414,6 @@
   </si>
   <si>
     <t>Value</t>
-  </si>
-  <si>
-    <t>Diode</t>
-  </si>
-  <si>
-    <t>Connector</t>
-  </si>
-  <si>
-    <t>Inductor</t>
-  </si>
-  <si>
-    <t>Resistor</t>
-  </si>
-  <si>
-    <t>Switch</t>
-  </si>
-  <si>
-    <t>Transistor</t>
-  </si>
-  <si>
-    <t>Capacitor</t>
-  </si>
-  <si>
-    <t>IC</t>
   </si>
   <si>
     <t>S:No</t>
@@ -453,7 +423,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,14 +435,6 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -494,7 +456,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,18 +465,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -552,51 +508,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom style="medium">
@@ -815,30 +726,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -847,6 +758,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -856,9 +770,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -868,38 +779,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1181,900 +1077,754 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" thickBot="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" ht="16.5" thickBot="1">
+      <c r="A1" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A2" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="9">
+      <c r="H3" s="6">
         <v>1</v>
       </c>
-      <c r="J3" s="9">
-        <f>I3*5</f>
-        <v>5</v>
-      </c>
-      <c r="K3" s="10">
+      <c r="I3" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1">
+    <row r="4" spans="1:9" ht="15.75" thickBot="1">
       <c r="A4" s="2">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="26" t="s">
+      <c r="B4" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A5" s="2">
+        <f t="shared" ref="A5:A25" si="0">A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A6" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A7" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="9">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A8" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="12">
+        <v>1</v>
+      </c>
+      <c r="I8" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A9" s="11">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1</v>
+      </c>
+      <c r="I9" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A10" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A11" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12">
+        <v>4</v>
+      </c>
+      <c r="I11" s="13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A12" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A13" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A14" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="5">
+        <v>4</v>
+      </c>
+      <c r="I14" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A15" s="2">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="5">
+        <v>5</v>
+      </c>
+      <c r="I15" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A16" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="5">
+        <v>5</v>
+      </c>
+      <c r="I16" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="9">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A19" s="2">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="B19" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="12">
+        <v>1</v>
+      </c>
+      <c r="I19" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A20" s="11">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="B20" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1</v>
+      </c>
+      <c r="I20" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A21" s="2">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="B21" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1</v>
+      </c>
+      <c r="I21" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="I4" s="7">
+      <c r="B22" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="7">
-        <f t="shared" ref="J4:J23" si="0">I4*5</f>
-        <v>5</v>
-      </c>
-      <c r="K4" s="11">
+      <c r="I22" s="8">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A5" s="2">
-        <f t="shared" ref="A5:A25" si="1">A4+1</f>
-        <v>3</v>
-      </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="26" t="s">
+    <row r="23" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A23" s="2">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="9">
+        <v>1</v>
+      </c>
+      <c r="I23" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A24" s="2">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="B24" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="6">
+        <v>1</v>
+      </c>
+      <c r="I24" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A25" s="2">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="7">
-        <v>1</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K5" s="11">
+      <c r="B25" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="9">
+        <v>10</v>
+      </c>
+      <c r="I25" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A6" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="7">
-        <v>2</v>
-      </c>
-      <c r="J6" s="7">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="K6" s="11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A7" s="2">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="12">
-        <v>1</v>
-      </c>
-      <c r="J7" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K7" s="13">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A8" s="2">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="15">
-        <v>1</v>
-      </c>
-      <c r="J8" s="15">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K8" s="16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A9" s="14">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="9">
-        <v>1</v>
-      </c>
-      <c r="J9" s="9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K9" s="10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A10" s="2">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="12">
-        <v>1</v>
-      </c>
-      <c r="J10" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K10" s="13">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A11" s="2">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15">
-        <v>4</v>
-      </c>
-      <c r="J11" s="15">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="K11" s="16">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A12" s="2">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I12" s="9">
-        <v>1</v>
-      </c>
-      <c r="J12" s="9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K12" s="10">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A13" s="2">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I13" s="7">
-        <v>1</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K13" s="11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A14" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" s="7">
-        <v>4</v>
-      </c>
-      <c r="J14" s="7">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="K14" s="11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A15" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="I15" s="7">
-        <v>5</v>
-      </c>
-      <c r="J15" s="7">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="K15" s="11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A16" s="2">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="I16" s="7">
-        <v>5</v>
-      </c>
-      <c r="J16" s="7">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="K16" s="11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A17" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="I17" s="7">
-        <v>1</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K17" s="11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A18" s="2">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="I18" s="12">
-        <v>1</v>
-      </c>
-      <c r="J18" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K18" s="13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A19" s="2">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="15">
-        <v>1</v>
-      </c>
-      <c r="J19" s="15">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K19" s="16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A20" s="14">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I20" s="9">
-        <v>1</v>
-      </c>
-      <c r="J20" s="9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K20" s="10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A21" s="2">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I21" s="7">
-        <v>1</v>
-      </c>
-      <c r="J21" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K21" s="11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A22" s="2">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="7">
-        <v>1</v>
-      </c>
-      <c r="J22" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K22" s="11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A23" s="2">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="12">
-        <v>1</v>
-      </c>
-      <c r="J23" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K23" s="13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A24" s="2">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I24" s="9">
-        <v>1</v>
-      </c>
-      <c r="J24" s="9">
-        <f>I24*5</f>
-        <v>5</v>
-      </c>
-      <c r="K24" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A25" s="2">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I25" s="12">
-        <v>10</v>
-      </c>
-      <c r="J25" s="12">
-        <f>I25*5</f>
-        <v>50</v>
-      </c>
-      <c r="K25" s="13">
-        <v>100</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B12:B18"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="I3:I25">
+  <conditionalFormatting sqref="H3:H25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/Deliverables/BOM/FLST_PCBWay BOM.xlsx
+++ b/Deliverables/BOM/FLST_PCBWay BOM.xlsx
@@ -1,30 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\flst\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\flst\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD71456-405C-4C87-943D-4BCB9D0CE288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7020"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="159">
   <si>
     <t>Designator</t>
   </si>
@@ -296,18 +305,6 @@
     <t>R10, R11, R12, R13, R16</t>
   </si>
   <si>
-    <t>RES SMD 200 OHM 0.5% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RT0603DRD07200RL</t>
-  </si>
-  <si>
-    <t>C700498</t>
-  </si>
-  <si>
-    <t>200R</t>
-  </si>
-  <si>
     <t>RF1</t>
   </si>
   <si>
@@ -410,20 +407,119 @@
     <t>C67112</t>
   </si>
   <si>
-    <t>Bill of Material (BOM) for Oliver</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>S:No</t>
+    <t>Component list</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project [Oliver_Flst.PrjPcb] (No PCB Document Selected)</t>
+  </si>
+  <si>
+    <t>Source Data From:</t>
+  </si>
+  <si>
+    <t>Oliver_Flst.PrjPcb</t>
+  </si>
+  <si>
+    <t>Project:</t>
+  </si>
+  <si>
+    <t>Variant:</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate Part No </t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>-----------</t>
+  </si>
+  <si>
+    <t>Kyocera AVX</t>
+  </si>
+  <si>
+    <t>Changzhou Huawei Elec</t>
+  </si>
+  <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>Yangzhou</t>
+  </si>
+  <si>
+    <t>XFCN</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>Wurth Electronics</t>
+  </si>
+  <si>
+    <t>Diodes</t>
+  </si>
+  <si>
+    <t>RALEC</t>
+  </si>
+  <si>
+    <t>Yageo Phycomp</t>
+  </si>
+  <si>
+    <t>RES SMD 536 OHM 1% 1/4W 1206</t>
+  </si>
+  <si>
+    <t>RES-1206</t>
+  </si>
+  <si>
+    <t>AC1206FR-07536RL</t>
+  </si>
+  <si>
+    <t>C229696</t>
+  </si>
+  <si>
+    <t>536R</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL</t>
+  </si>
+  <si>
+    <t>XKB</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>Microchip</t>
+  </si>
+  <si>
+    <t>Vishay Lite-On</t>
+  </si>
+  <si>
+    <t>CEL</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Notes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+  </numFmts>
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,15 +544,116 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color indexed="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,8 +666,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF03A4CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -516,40 +731,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -559,123 +742,69 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -685,12 +814,32 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -698,25 +847,71 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -726,76 +921,169 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -812,6 +1100,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28576</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2000250" cy="1114424"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF3EE1E3-21D1-452F-8329-CDB16A41A077}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12068176" y="638176"/>
+          <a:ext cx="2000250" cy="1114424"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1076,767 +1413,1074 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F53BE94E-0DF2-434E-9FA4-66DB64B1F05A}">
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5703125" customWidth="1"/>
+    <col min="5" max="5" width="27.42578125" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="43"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="38"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A2" s="1" t="s">
+      <c r="D4" s="44"/>
+      <c r="E4" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="40"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="44"/>
+      <c r="E5" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="40"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="40"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="40"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="42"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F9" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G9" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="J9" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="L9" s="25" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A3" s="2">
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1">
+        <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C10" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="E10" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="26">
+        <v>1</v>
+      </c>
+      <c r="L10" s="51">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="6">
+    </row>
+    <row r="11" spans="1:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1">
+        <f t="shared" ref="B11:B31" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="28">
         <v>1</v>
       </c>
-      <c r="I3" s="7">
+      <c r="L11" s="52">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A4" s="2">
-        <f>A3+1</f>
-        <v>2</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="5">
+    <row r="12" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="26">
         <v>1</v>
       </c>
-      <c r="I4" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A5" s="2">
-        <f t="shared" ref="A5:A25" si="0">A4+1</f>
-        <v>3</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8">
+      <c r="L12" s="51">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A6" s="2">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="C13" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E13" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F13" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G13" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="J13" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="5">
+      <c r="K13" s="28">
         <v>2</v>
       </c>
-      <c r="I6" s="8">
+      <c r="L13" s="52">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A7" s="2">
-        <f t="shared" si="0"/>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1">
+        <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="C14" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E14" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F14" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G14" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="I14" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="J14" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="9">
+      <c r="K14" s="26">
         <v>1</v>
       </c>
-      <c r="I7" s="10">
+      <c r="L14" s="51">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A8" s="2">
+    <row r="15" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="C15" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="E15" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F15" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G15" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="J15" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="12">
+      <c r="K15" s="28">
         <v>1</v>
       </c>
-      <c r="I8" s="13">
+      <c r="L15" s="52">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A9" s="11">
-        <f t="shared" si="0"/>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="1">
+        <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="6">
+      <c r="C16" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H16" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="I16" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="26">
         <v>1</v>
       </c>
-      <c r="I9" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A10" s="2">
+      <c r="L16" s="51">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="C17" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="28">
+        <v>1</v>
+      </c>
+      <c r="L17" s="52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="1">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E18" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F18" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G18" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="J18" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="9">
+      <c r="K18" s="26">
         <v>1</v>
       </c>
-      <c r="I10" s="10">
+      <c r="L18" s="51">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12">
-        <v>4</v>
-      </c>
-      <c r="I11" s="13">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A12" s="2">
+    <row r="19" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="6">
-        <v>1</v>
-      </c>
-      <c r="I12" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A13" s="2">
-        <f t="shared" si="0"/>
+      <c r="C19" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="30">
+        <v>61300211121</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="K19" s="28">
+        <v>10</v>
+      </c>
+      <c r="L19" s="52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="1">
+        <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H13" s="5">
-        <v>1</v>
-      </c>
-      <c r="I13" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A14" s="2">
+      <c r="C20" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="27"/>
+      <c r="K20" s="26">
+        <v>4</v>
+      </c>
+      <c r="L20" s="51">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="5">
-        <v>4</v>
-      </c>
-      <c r="I14" s="8">
+      <c r="C21" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="J21" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21" s="28">
+        <v>1</v>
+      </c>
+      <c r="L21" s="52">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="1">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K22" s="26">
+        <v>1</v>
+      </c>
+      <c r="L22" s="51">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A15" s="2">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="5">
-        <v>5</v>
-      </c>
-      <c r="I15" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A16" s="2">
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="C23" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J23" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="28">
+        <v>4</v>
+      </c>
+      <c r="L23" s="52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="1">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="5">
+      <c r="F24" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="I24" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="J24" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" s="26">
         <v>5</v>
       </c>
-      <c r="I16" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A17" s="2">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" s="5">
-        <v>1</v>
-      </c>
-      <c r="I17" s="8">
+      <c r="L24" s="51">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A18" s="2">
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="C25" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="J25" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="K25" s="28">
+        <v>5</v>
+      </c>
+      <c r="L25" s="52">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="1">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="J26" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="K26" s="26">
+        <v>1</v>
+      </c>
+      <c r="L26" s="51">
         <v>100</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="H18" s="9">
-        <v>1</v>
-      </c>
-      <c r="I18" s="10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A19" s="2">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="12">
-        <v>1</v>
-      </c>
-      <c r="I19" s="13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A20" s="11">
+    </row>
+    <row r="27" spans="1:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="C27" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H27" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="K27" s="28">
+        <v>1</v>
+      </c>
+      <c r="L27" s="52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="1">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H28" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="I28" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="J28" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="6">
+      <c r="K28" s="26">
         <v>1</v>
       </c>
-      <c r="I20" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A21" s="2">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="5">
-        <v>1</v>
-      </c>
-      <c r="I21" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A22" s="2">
+      <c r="L28" s="51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="C29" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="J29" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="5">
+      <c r="K29" s="28">
         <v>1</v>
       </c>
-      <c r="I22" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A23" s="2">
-        <f t="shared" si="0"/>
+      <c r="L29" s="52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="1">
+        <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G23" s="9" t="s">
+      <c r="C30" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H30" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="J30" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="H23" s="9">
+      <c r="K30" s="26">
         <v>1</v>
       </c>
-      <c r="I23" s="10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A24" s="2">
+      <c r="L30" s="51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="6">
+      <c r="C31" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H31" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="K31" s="28">
         <v>1</v>
       </c>
-      <c r="I24" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A25" s="2">
-        <f t="shared" si="0"/>
+      <c r="L31" s="52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="1">
+        <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H25" s="9">
-        <v>10</v>
-      </c>
-      <c r="I25" s="10">
-        <v>100</v>
-      </c>
+      <c r="C32" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="H32" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="I32" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="J32" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="K32" s="31">
+        <v>1</v>
+      </c>
+      <c r="L32" s="53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" s="55"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="58"/>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="59"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+  <mergeCells count="4">
+    <mergeCell ref="F33:L34"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="K3:K8"/>
   </mergeCells>
-  <conditionalFormatting sqref="H3:H25">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/FLST_PCBWay BOM.xlsx
+++ b/Deliverables/BOM/FLST_PCBWay BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\flst\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD71456-405C-4C87-943D-4BCB9D0CE288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70144D4-DC3E-41AC-8A95-0A79B9A9BC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="157">
   <si>
     <t>Designator</t>
   </si>
@@ -431,16 +431,10 @@
     <t>#</t>
   </si>
   <si>
-    <t xml:space="preserve">Alternate Part No </t>
-  </si>
-  <si>
     <t>Manufacturer</t>
   </si>
   <si>
     <t>Comment</t>
-  </si>
-  <si>
-    <t>-----------</t>
   </si>
   <si>
     <t>Kyocera AVX</t>
@@ -519,7 +513,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -644,14 +638,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -685,7 +671,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -917,6 +903,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -931,9 +930,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -996,9 +992,6 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1020,24 +1013,6 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1084,6 +1059,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1106,7 +1105,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>57151</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>28576</xdr:rowOff>
@@ -1414,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F53BE94E-0DF2-434E-9FA4-66DB64B1F05A}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -1422,14 +1421,13 @@
     <col min="4" max="4" width="31.5703125" customWidth="1"/>
     <col min="5" max="5" width="27.42578125" customWidth="1"/>
     <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="4"/>
@@ -1438,125 +1436,117 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+    </row>
+    <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="6"/>
+      <c r="E2" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F2" s="9"/>
+      <c r="F2" s="8"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="43"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="35"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="44" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45" t="s">
+      <c r="D3" s="36"/>
+      <c r="E3" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="38"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F3" s="36"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="54"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="44" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="13" t="s">
+      <c r="D4" s="36"/>
+      <c r="E4" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="14"/>
+      <c r="F4" s="13"/>
       <c r="G4" s="14"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="40"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="55"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="44" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="36"/>
+      <c r="E5" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="40"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F5" s="16"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="55"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="40"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="55"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="40"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="20"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="55"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="42"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="22"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="56"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="1" t="s">
         <v>131</v>
@@ -1570,915 +1560,841 @@
       <c r="E9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="23" t="s">
         <v>3</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="25" t="s">
+      <c r="K9" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="1">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>136</v>
+      <c r="G10" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>11</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="26">
+      <c r="J10" s="25">
         <v>1</v>
       </c>
-      <c r="L10" s="51">
+      <c r="K10" s="43">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="1">
         <f t="shared" ref="B11:B31" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="H11" s="29" t="s">
-        <v>137</v>
+      <c r="H11" s="27" t="s">
+        <v>17</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="28">
+      <c r="J11" s="27">
         <v>1</v>
       </c>
-      <c r="L11" s="52">
+      <c r="K11" s="44">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="1">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H12" s="27" t="s">
-        <v>138</v>
+      <c r="G12" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="26">
+      <c r="J12" s="25">
         <v>1</v>
       </c>
-      <c r="L12" s="51">
+      <c r="K12" s="43">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>138</v>
+      <c r="G13" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="28">
+      <c r="J13" s="27">
         <v>2</v>
       </c>
-      <c r="L13" s="52">
+      <c r="K13" s="44">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="1">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H14" s="27" t="s">
-        <v>138</v>
+      <c r="G14" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>33</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="K14" s="26">
+      <c r="J14" s="25">
         <v>1</v>
       </c>
-      <c r="L14" s="51">
+      <c r="K14" s="43">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>139</v>
+      <c r="G15" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>39</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="K15" s="28">
+      <c r="J15" s="27">
         <v>1</v>
       </c>
-      <c r="L15" s="52">
+      <c r="K15" s="44">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="1">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>140</v>
+      <c r="G16" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="K16" s="26">
+      <c r="J16" s="25">
         <v>1</v>
       </c>
-      <c r="L16" s="51">
+      <c r="K16" s="43">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>141</v>
+      <c r="G17" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>50</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="K17" s="28">
+      <c r="J17" s="27">
         <v>1</v>
       </c>
-      <c r="L17" s="52">
+      <c r="K17" s="44">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="1">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E18" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H18" s="27" t="s">
-        <v>141</v>
+      <c r="G18" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>56</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="J18" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="26">
+      <c r="J18" s="25">
         <v>1</v>
       </c>
-      <c r="L18" s="51">
+      <c r="K18" s="43">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="30">
-        <v>61300211121</v>
-      </c>
-      <c r="G19" s="28" t="s">
+      <c r="F19" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="H19" s="29" t="s">
-        <v>142</v>
+      <c r="G19" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="I19" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="J19" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="K19" s="28">
+      <c r="J19" s="27">
         <v>10</v>
       </c>
-      <c r="L19" s="52">
+      <c r="K19" s="44">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="1">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="G20" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H20" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="I20" s="26" t="s">
+      <c r="G20" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="H20" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="J20" s="27"/>
-      <c r="K20" s="26">
+      <c r="I20" s="26"/>
+      <c r="J20" s="25">
         <v>4</v>
       </c>
-      <c r="L20" s="51">
+      <c r="K20" s="43">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>144</v>
+      <c r="G21" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="27" t="s">
+        <v>71</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="J21" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="K21" s="28">
+      <c r="J21" s="27">
         <v>1</v>
       </c>
-      <c r="L21" s="52">
+      <c r="K21" s="44">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="1">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="G22" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>138</v>
+      <c r="G22" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>76</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="J22" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="K22" s="26">
+      <c r="J22" s="25">
         <v>1</v>
       </c>
-      <c r="L22" s="51">
+      <c r="K22" s="43">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="G23" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>138</v>
+      <c r="G23" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>82</v>
       </c>
       <c r="I23" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="J23" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="K23" s="28">
+      <c r="J23" s="27">
         <v>4</v>
       </c>
-      <c r="L23" s="52">
+      <c r="K23" s="44">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="1">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="F24" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H24" s="27" t="s">
-        <v>145</v>
+      <c r="G24" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="H24" s="25" t="s">
+        <v>87</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="J24" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="K24" s="26">
+      <c r="J24" s="25">
         <v>5</v>
       </c>
-      <c r="L24" s="51">
+      <c r="K24" s="43">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="G25" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="H25" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="I25" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="G25" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="I25" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="J25" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="K25" s="28">
+      <c r="J25" s="27">
         <v>5</v>
       </c>
-      <c r="L25" s="52">
+      <c r="K25" s="44">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="1">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="E26" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F26" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="G26" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H26" s="27" t="s">
-        <v>138</v>
+      <c r="G26" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H26" s="25" t="s">
+        <v>93</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="J26" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="K26" s="26">
+      <c r="J26" s="25">
         <v>1</v>
       </c>
-      <c r="L26" s="51">
+      <c r="K26" s="43">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="G27" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>151</v>
+      <c r="G27" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="H27" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="J27" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="K27" s="28">
+      <c r="J27" s="27">
         <v>1</v>
       </c>
-      <c r="L27" s="52">
+      <c r="K27" s="44">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="1">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F28" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H28" s="27" t="s">
-        <v>152</v>
+      <c r="G28" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="H28" s="25" t="s">
+        <v>103</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="J28" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="K28" s="26">
+      <c r="J28" s="25">
         <v>1</v>
       </c>
-      <c r="L28" s="51">
+      <c r="K28" s="43">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="29" t="s">
+      <c r="F29" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="G29" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>153</v>
+      <c r="G29" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="H29" s="27" t="s">
+        <v>108</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="J29" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="K29" s="28">
+      <c r="J29" s="27">
         <v>1</v>
       </c>
-      <c r="L29" s="52">
+      <c r="K29" s="44">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="1">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G30" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="H30" s="27" t="s">
-        <v>154</v>
+      <c r="G30" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="H30" s="25" t="s">
+        <v>113</v>
       </c>
       <c r="I30" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="J30" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="K30" s="26">
+      <c r="J30" s="25">
         <v>1</v>
       </c>
-      <c r="L30" s="51">
+      <c r="K30" s="43">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="E31" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="F31" s="29" t="s">
+      <c r="F31" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="G31" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H31" s="29" t="s">
-        <v>155</v>
+      <c r="G31" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="H31" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="I31" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="J31" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="K31" s="28">
+      <c r="J31" s="27">
         <v>1</v>
       </c>
-      <c r="L31" s="52">
+      <c r="K31" s="44">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="1">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="D32" s="31" t="s">
+      <c r="D32" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="31" t="s">
+      <c r="E32" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="F32" s="32" t="s">
+      <c r="F32" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="G32" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="H32" s="32" t="s">
+      <c r="G32" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="I32" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="29">
+        <v>1</v>
+      </c>
+      <c r="K32" s="45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" s="47"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="50"/>
+    </row>
+    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="I32" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="J32" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="K32" s="31">
-        <v>1</v>
-      </c>
-      <c r="L32" s="53">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="54" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="55"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="58"/>
-    </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="59"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="60"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="F33:L34"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="F33:K34"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K3:K8"/>
+    <mergeCell ref="J3:J8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Deliverables/BOM/FLST_PCBWay BOM.xlsx
+++ b/Deliverables/BOM/FLST_PCBWay BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\flst\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70144D4-DC3E-41AC-8A95-0A79B9A9BC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614B6B70-2A9C-49DB-A515-7DBE31ABA526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>LCSC/Part No</t>
   </si>
   <si>
-    <t>Quantity</t>
-  </si>
-  <si>
     <t>LCSC/MOQ/5 Boards</t>
   </si>
   <si>
@@ -504,6 +501,9 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Quantity (Per Board)</t>
   </si>
 </sst>
 </file>
@@ -1048,6 +1048,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1080,9 +1083,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1106,11 +1106,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>57151</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>28576</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2000250" cy="1114424"/>
+    <xdr:ext cx="2686049" cy="1114424"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
@@ -1137,8 +1137,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12068176" y="638176"/>
-          <a:ext cx="2000250" cy="1114424"/>
+          <a:off x="10934700" y="638176"/>
+          <a:ext cx="2686049" cy="1114424"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1424,6 +1424,7 @@
     <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1436,18 +1437,18 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
@@ -1460,52 +1461,52 @@
       <c r="A3" s="2"/>
       <c r="B3" s="10"/>
       <c r="C3" s="36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F3" s="36"/>
       <c r="G3" s="38"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="54"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="55"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="10"/>
       <c r="C4" s="36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D4" s="36"/>
       <c r="E4" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="55"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="10"/>
       <c r="C5" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" s="36"/>
       <c r="E5" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="55"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="56"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -1517,8 +1518,8 @@
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="55"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="56"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -1530,8 +1531,8 @@
       <c r="G7" s="40"/>
       <c r="H7" s="40"/>
       <c r="I7" s="40"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="55"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="56"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
@@ -1543,13 +1544,13 @@
       <c r="G8" s="40"/>
       <c r="H8" s="40"/>
       <c r="I8" s="40"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="56"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="57"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>0</v>
@@ -1564,19 +1565,19 @@
         <v>3</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K9" s="24" t="s">
         <v>5</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1586,25 +1587,25 @@
         <v>1</v>
       </c>
       <c r="C10" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="E10" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="F10" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="G10" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="H10" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="H10" s="25" t="s">
+      <c r="I10" s="26" t="s">
         <v>11</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>12</v>
       </c>
       <c r="J10" s="25">
         <v>1</v>
@@ -1620,25 +1621,25 @@
         <v>2</v>
       </c>
       <c r="C11" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="E11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="F11" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="G11" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="H11" s="27" t="s">
+      <c r="I11" s="28" t="s">
         <v>17</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>18</v>
       </c>
       <c r="J11" s="27">
         <v>1</v>
@@ -1654,25 +1655,25 @@
         <v>3</v>
       </c>
       <c r="C12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="E12" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="F12" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="G12" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H12" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="H12" s="25" t="s">
+      <c r="I12" s="26" t="s">
         <v>23</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>24</v>
       </c>
       <c r="J12" s="25">
         <v>1</v>
@@ -1688,25 +1689,25 @@
         <v>4</v>
       </c>
       <c r="C13" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="E13" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="28" t="s">
+      <c r="G13" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="H13" s="27" t="s">
+      <c r="I13" s="28" t="s">
         <v>28</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>29</v>
       </c>
       <c r="J13" s="27">
         <v>2</v>
@@ -1722,25 +1723,25 @@
         <v>5</v>
       </c>
       <c r="C14" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="E14" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="26" t="s">
+      <c r="G14" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="H14" s="25" t="s">
+      <c r="I14" s="26" t="s">
         <v>33</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>34</v>
       </c>
       <c r="J14" s="25">
         <v>1</v>
@@ -1756,25 +1757,25 @@
         <v>6</v>
       </c>
       <c r="C15" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="E15" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="F15" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="G15" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="H15" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="H15" s="27" t="s">
+      <c r="I15" s="28" t="s">
         <v>39</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>40</v>
       </c>
       <c r="J15" s="27">
         <v>1</v>
@@ -1790,25 +1791,25 @@
         <v>7</v>
       </c>
       <c r="C16" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="E16" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="F16" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="G16" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="H16" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="H16" s="25" t="s">
+      <c r="I16" s="26" t="s">
         <v>45</v>
-      </c>
-      <c r="I16" s="26" t="s">
-        <v>46</v>
       </c>
       <c r="J16" s="25">
         <v>1</v>
@@ -1824,25 +1825,25 @@
         <v>8</v>
       </c>
       <c r="C17" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="28" t="s">
+      <c r="G17" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="H17" s="27" t="s">
+      <c r="I17" s="28" t="s">
         <v>50</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>51</v>
       </c>
       <c r="J17" s="27">
         <v>1</v>
@@ -1858,25 +1859,25 @@
         <v>9</v>
       </c>
       <c r="C18" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="E18" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="F18" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="G18" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>56</v>
-      </c>
       <c r="I18" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J18" s="25">
         <v>1</v>
@@ -1892,25 +1893,25 @@
         <v>10</v>
       </c>
       <c r="C19" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="E19" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="F19" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="60" t="s">
+      <c r="G19" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="H19" s="27" t="s">
-        <v>61</v>
-      </c>
       <c r="I19" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J19" s="27">
         <v>10</v>
@@ -1926,22 +1927,22 @@
         <v>11</v>
       </c>
       <c r="C20" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="E20" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="F20" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="G20" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" s="25" t="s">
         <v>65</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>66</v>
       </c>
       <c r="I20" s="26"/>
       <c r="J20" s="25">
@@ -1958,25 +1959,25 @@
         <v>12</v>
       </c>
       <c r="C21" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="E21" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="F21" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="G21" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="H21" s="27" t="s">
+      <c r="I21" s="28" t="s">
         <v>71</v>
-      </c>
-      <c r="I21" s="28" t="s">
-        <v>72</v>
       </c>
       <c r="J21" s="27">
         <v>1</v>
@@ -1992,25 +1993,25 @@
         <v>13</v>
       </c>
       <c r="C22" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="E22" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="26" t="s">
+      <c r="G22" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H22" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="G22" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="H22" s="25" t="s">
+      <c r="I22" s="26" t="s">
         <v>76</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>77</v>
       </c>
       <c r="J22" s="25">
         <v>1</v>
@@ -2026,25 +2027,25 @@
         <v>14</v>
       </c>
       <c r="C23" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="E23" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="F23" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="G23" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="G23" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="H23" s="27" t="s">
+      <c r="I23" s="28" t="s">
         <v>82</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>83</v>
       </c>
       <c r="J23" s="27">
         <v>4</v>
@@ -2060,25 +2061,25 @@
         <v>15</v>
       </c>
       <c r="C24" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="E24" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="F24" s="26" t="s">
+      <c r="G24" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="H24" s="25" t="s">
+      <c r="I24" s="26" t="s">
         <v>87</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>88</v>
       </c>
       <c r="J24" s="25">
         <v>5</v>
@@ -2094,25 +2095,25 @@
         <v>16</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D25" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="F25" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="G25" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="G25" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="H25" s="27" t="s">
+      <c r="I25" s="28" t="s">
         <v>147</v>
-      </c>
-      <c r="I25" s="28" t="s">
-        <v>148</v>
       </c>
       <c r="J25" s="27">
         <v>5</v>
@@ -2128,25 +2129,25 @@
         <v>17</v>
       </c>
       <c r="C26" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="E26" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" s="26" t="s">
+      <c r="G26" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H26" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="G26" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="H26" s="25" t="s">
+      <c r="I26" s="26" t="s">
         <v>93</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>94</v>
       </c>
       <c r="J26" s="25">
         <v>1</v>
@@ -2162,25 +2163,25 @@
         <v>18</v>
       </c>
       <c r="C27" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="E27" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27" s="28" t="s">
+      <c r="G27" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="H27" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="G27" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="H27" s="27" t="s">
+      <c r="I27" s="28" t="s">
         <v>98</v>
-      </c>
-      <c r="I27" s="28" t="s">
-        <v>99</v>
       </c>
       <c r="J27" s="27">
         <v>1</v>
@@ -2196,25 +2197,25 @@
         <v>19</v>
       </c>
       <c r="C28" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="E28" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="26" t="s">
+      <c r="G28" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="H28" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="H28" s="25" t="s">
-        <v>103</v>
-      </c>
       <c r="I28" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J28" s="25">
         <v>1</v>
@@ -2230,25 +2231,25 @@
         <v>20</v>
       </c>
       <c r="C29" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="E29" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="27" t="s">
+      <c r="F29" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="G29" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="H29" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="G29" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="H29" s="27" t="s">
-        <v>108</v>
-      </c>
       <c r="I29" s="28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J29" s="27">
         <v>1</v>
@@ -2264,25 +2265,25 @@
         <v>21</v>
       </c>
       <c r="C30" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="E30" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="F30" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="G30" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="G30" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="H30" s="25" t="s">
-        <v>113</v>
-      </c>
       <c r="I30" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J30" s="25">
         <v>1</v>
@@ -2298,25 +2299,25 @@
         <v>22</v>
       </c>
       <c r="C31" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="E31" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="F31" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="G31" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="G31" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="H31" s="27" t="s">
-        <v>118</v>
-      </c>
       <c r="I31" s="28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J31" s="27">
         <v>1</v>
@@ -2332,25 +2333,25 @@
         <v>23</v>
       </c>
       <c r="C32" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="E32" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="29" t="s">
+      <c r="F32" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="G32" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H32" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="G32" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>123</v>
-      </c>
       <c r="I32" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J32" s="29">
         <v>1</v>
@@ -2363,31 +2364,31 @@
       <c r="A33" s="2"/>
       <c r="B33" s="31"/>
       <c r="C33" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="48"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="51"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="32"/>
       <c r="C34" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D34" s="34"/>
       <c r="E34" s="34"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="51"/>
-      <c r="K34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="4">
